--- a/output/laminas_comunales/comunal_i_ingr_a_2024_atacama.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_a_2024_atacama.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -405,9 +400,6 @@
       <c r="E2">
         <v>3.090923505483478</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -427,9 +419,6 @@
       <c r="E3">
         <v>5.606781597217636</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -449,9 +438,6 @@
       <c r="E4">
         <v>6.060375993785794</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -471,9 +457,6 @@
       <c r="E5">
         <v>6.293283835897556</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -493,9 +476,6 @@
       <c r="E6">
         <v>4.014392534326294</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -515,9 +495,6 @@
       <c r="E7">
         <v>3.690990531780125</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -537,9 +514,6 @@
       <c r="E8">
         <v>5.687789325716142</v>
       </c>
-      <c r="F8" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -559,9 +533,6 @@
       <c r="E9">
         <v>8.395049373974883</v>
       </c>
-      <c r="F9" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -580,9 +551,6 @@
       </c>
       <c r="E10">
         <v>8.261619468112901</v>
-      </c>
-      <c r="F10" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_ingr_a_2024_atacama.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_a_2024_atacama.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -442,114 +442,133 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Vallenar</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B5">
-        <v>1382958</v>
+        <v>1387892.38</v>
       </c>
       <c r="C5">
-        <v>1301077.5</v>
+        <v>1315357.25</v>
       </c>
       <c r="D5">
-        <v>81880.5</v>
+        <v>72535.12999999989</v>
       </c>
       <c r="E5">
-        <v>6.293283835897556</v>
+        <v>5.51448133197272</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Caldera</t>
+          <t>Vallenar</t>
         </is>
       </c>
       <c r="B6">
-        <v>1352200.5</v>
+        <v>1382958</v>
       </c>
       <c r="C6">
-        <v>1300012.88</v>
+        <v>1301077.5</v>
       </c>
       <c r="D6">
-        <v>52187.62000000011</v>
+        <v>81880.5</v>
       </c>
       <c r="E6">
-        <v>4.014392534326294</v>
+        <v>6.293283835897556</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Chañaral</t>
+          <t>Caldera</t>
         </is>
       </c>
       <c r="B7">
-        <v>1294072.5</v>
+        <v>1352200.5</v>
       </c>
       <c r="C7">
-        <v>1248008.62</v>
+        <v>1300012.88</v>
       </c>
       <c r="D7">
-        <v>46063.87999999989</v>
+        <v>52187.62000000011</v>
       </c>
       <c r="E7">
-        <v>3.690990531780125</v>
+        <v>4.014392534326294</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Freirina</t>
+          <t>Chañaral</t>
         </is>
       </c>
       <c r="B8">
-        <v>1190560</v>
+        <v>1294072.5</v>
       </c>
       <c r="C8">
-        <v>1126487.75</v>
+        <v>1248008.62</v>
       </c>
       <c r="D8">
-        <v>64072.25</v>
+        <v>46063.87999999989</v>
       </c>
       <c r="E8">
-        <v>5.687789325716142</v>
+        <v>3.690990531780125</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Tierra Amarilla</t>
+          <t>Freirina</t>
         </is>
       </c>
       <c r="B9">
-        <v>1186086</v>
+        <v>1190560</v>
       </c>
       <c r="C9">
-        <v>1094225.25</v>
+        <v>1126487.75</v>
       </c>
       <c r="D9">
-        <v>91860.75</v>
+        <v>64072.25</v>
       </c>
       <c r="E9">
-        <v>8.395049373974883</v>
+        <v>5.687789325716142</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Tierra Amarilla</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>1186086</v>
+      </c>
+      <c r="C10">
+        <v>1094225.25</v>
+      </c>
+      <c r="D10">
+        <v>91860.75</v>
+      </c>
+      <c r="E10">
+        <v>8.395049373974883</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Alto del Carmen</t>
         </is>
       </c>
-      <c r="B10">
+      <c r="B11">
         <v>1098097</v>
       </c>
-      <c r="C10">
+      <c r="C11">
         <v>1014299.44</v>
       </c>
-      <c r="D10">
+      <c r="D11">
         <v>83797.56000000006</v>
       </c>
-      <c r="E10">
+      <c r="E11">
         <v>8.261619468112901</v>
       </c>
     </row>

--- a/output/laminas_comunales/comunal_i_ingr_a_2024_atacama.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_a_2024_atacama.xlsx
@@ -579,7 +579,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -588,11 +588,6 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -600,28 +595,19 @@
           <t>Alto del Carmen</t>
         </is>
       </c>
-      <c r="B2">
-        <v>1098097</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Caldera</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>1352200.5</v>
+          <t>Freirina</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Chañaral</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>1294072.5</v>
+          <t>Huasco</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -630,48 +616,33 @@
           <t>Copiapó</t>
         </is>
       </c>
-      <c r="B5">
-        <v>1419013.38</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Diego de Almagro</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>1476402.62</v>
+          <t>Caldera</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Freirina</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>1190560</v>
+          <t>Chañaral</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Huasco</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>1392214.38</v>
+          <t>Tierra Amarilla</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Tierra Amarilla</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>1186086</v>
+          <t>Diego de Almagro</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -679,9 +650,6 @@
         <is>
           <t>Vallenar</t>
         </is>
-      </c>
-      <c r="B10">
-        <v>1382958</v>
       </c>
     </row>
   </sheetData>
